--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512410_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512410_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>J. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1203</v>
+        <v>3.5095</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9064</v>
+        <v>1.8091</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2139</v>
+        <v>1.7005</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8788</v>
+        <v>3.1997</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4129</v>
+        <v>3.4972</v>
       </c>
       <c r="I2" t="n">
-        <v>0.466</v>
+        <v>-0.2974</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8384</v>
+        <v>3.9843</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7199</v>
+        <v>2.7446</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1185</v>
+        <v>1.2396</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0404</v>
+        <v>-0.7845</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.307</v>
+        <v>0.7526</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3474</v>
+        <v>-1.5371</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.4339</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8194</v>
+        <v>2.227</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7239</v>
+        <v>0.3098</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3698</v>
+        <v>0.0518</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3541</v>
+        <v>0.258</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9515</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9515</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MARIN ORTEGA</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0033</v>
+        <v>2.8468</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2045</v>
+        <v>1.97</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7988</v>
+        <v>0.8767</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1677</v>
+        <v>0.883</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4652</v>
+        <v>0.4338</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2974</v>
+        <v>0.4492</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8996</v>
+        <v>0.8877</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6851</v>
+        <v>0.7684</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2145</v>
+        <v>0.1193</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7319</v>
+        <v>-0.0047</v>
       </c>
       <c r="N3" t="n">
-        <v>0.78</v>
+        <v>-0.3346</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5119</v>
+        <v>0.33</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2533</v>
+        <v>0.8098</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1644</v>
+        <v>0.4054</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4418</v>
+        <v>0.3338</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2774</v>
+        <v>0.0716</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.9755</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.9755</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8197</v>
+        <v>2.821</v>
       </c>
       <c r="E4" t="n">
-        <v>3.404</v>
+        <v>3.3464</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5843</v>
+        <v>-0.5254</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0743</v>
+        <v>1.0945</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4633</v>
+        <v>1.4628</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.389</v>
+        <v>-0.3683</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9684</v>
+        <v>2.0352</v>
       </c>
       <c r="K4" t="n">
-        <v>0.962</v>
+        <v>0.9871</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0064</v>
+        <v>1.0481</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8941</v>
+        <v>-0.9407</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5013</v>
+        <v>0.4757</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3954</v>
+        <v>-1.4164</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5163</v>
+        <v>0.5118</v>
       </c>
       <c r="T4" t="n">
-        <v>0.255</v>
+        <v>0.121</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2613</v>
+        <v>0.3908</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Z. WILLIAMS</t>
+          <t>J. JIMENEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3024</v>
+        <v>2.2304</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5133</v>
+        <v>0.405</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2109</v>
+        <v>1.8253</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2799</v>
+        <v>0.7292</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6205</v>
+        <v>0.5159</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6593</v>
+        <v>0.2133</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0901</v>
+        <v>1.8483</v>
       </c>
       <c r="K5" t="n">
-        <v>3.0111</v>
+        <v>0.9285</v>
       </c>
       <c r="L5" t="n">
-        <v>0.079</v>
+        <v>0.9198</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1897</v>
+        <v>-1.1192</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3906</v>
+        <v>-0.4126</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5803</v>
+        <v>-0.7066</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4097</v>
+        <v>1.2147</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8194</v>
+        <v>2.4294</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4452</v>
+        <v>0.2865</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0005</v>
+        <v>-0.2286</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4447</v>
+        <v>0.5151</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.013</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3482</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. JIMENEZ GONZALEZ</t>
+          <t>Z. WILLIAMS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0847</v>
+        <v>1.401</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2943</v>
+        <v>1.9591</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3789</v>
+        <v>-0.5581</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7307</v>
+        <v>3.2983</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5541</v>
+        <v>2.6474</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1766</v>
+        <v>0.6509</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7696</v>
+        <v>3.1409</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9172</v>
+        <v>3.0614</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8524</v>
+        <v>0.0795</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0389</v>
+        <v>0.1575</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3631</v>
+        <v>-0.4139</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6758</v>
+        <v>0.5714</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2291</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4582</v>
+        <v>0.8098</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1249</v>
+        <v>0.5438</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8348</v>
+        <v>0.3771</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9597</v>
+        <v>0.1667</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.0362</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3442</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8683</v>
+        <v>1.0288</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2123</v>
+        <v>0.1666</v>
       </c>
       <c r="F7" t="n">
-        <v>0.656</v>
+        <v>0.8622</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3548</v>
+        <v>1.3511</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6269</v>
+        <v>0.6135</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7279</v>
+        <v>0.7376</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8258</v>
+        <v>1.8552</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0988</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7282</v>
+        <v>1.7565</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4709</v>
+        <v>-0.5041</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5294</v>
+        <v>0.5147</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0003</v>
+        <v>-1.0188</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4865</v>
+        <v>-0.3223</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1073</v>
+        <v>0.012</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5938</v>
+        <v>-0.3343</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="8">
@@ -1033,31 +1033,31 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5259</v>
+        <v>-0.5371</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2224</v>
+        <v>0.125</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6965</v>
+        <v>-0.6621</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4217</v>
+        <v>1.6437</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7568</v>
+        <v>1.6997</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3351</v>
+        <v>-0.056</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4881</v>
+        <v>2.5026</v>
       </c>
       <c r="K9" t="n">
-        <v>2.172</v>
+        <v>1.9551</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3161</v>
+        <v>0.5476</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0664</v>
+        <v>-0.8589</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5849</v>
+        <v>-0.2553</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6512</v>
+        <v>-0.6036</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.2533</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.097</v>
+        <v>-2.227</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8436</v>
+        <v>1.4172</v>
       </c>
       <c r="S9" t="n">
-        <v>0.412</v>
+        <v>-0.1808</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5073</v>
+        <v>-0.1507</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9192</v>
+        <v>-0.0301</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1062</v>
+        <v>-1.1902</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1062</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4393</v>
+        <v>-0.6485</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9872</v>
+        <v>-1.8322</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4521</v>
+        <v>1.1837</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9095</v>
+        <v>1.4094</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7751</v>
+        <v>2.7669</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6846</v>
+        <v>-1.3575</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6921</v>
+        <v>2.5299</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0058</v>
+        <v>2.2119</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6863</v>
+        <v>0.318</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2175</v>
+        <v>-1.1205</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7809</v>
+        <v>0.555</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9984</v>
+        <v>-1.6755</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6145</v>
+        <v>-2.227</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0242</v>
+        <v>-4.049</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4097</v>
+        <v>1.8221</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1439</v>
+        <v>0.2623</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.655</v>
+        <v>-0.2199</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.489</v>
+        <v>0.4821</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5903</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4464</v>
+        <v>-0.9133</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.464</v>
+        <v>-0.7265</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-0.1868</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6303</v>
+        <v>0.896</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6948</v>
+        <v>-0.7899</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0645</v>
+        <v>1.686</v>
       </c>
       <c r="J11" t="n">
-        <v>2.436</v>
+        <v>0.7184</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9183</v>
+        <v>0.0191</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5177</v>
+        <v>0.6993</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8057</v>
+        <v>0.1776</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2235</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5822000000000001</v>
+        <v>0.9866</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8194</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2533</v>
+        <v>-1.0123</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4339</v>
+        <v>0.4049</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0766</v>
+        <v>-0.6069</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6466</v>
+        <v>-0.4327</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.43</v>
+        <v>-0.1742</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1806</v>
+        <v>-0.5951</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1806</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8702</v>
+        <v>-2.4442</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2928</v>
+        <v>-0.9689</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5774</v>
+        <v>-1.4753</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4542</v>
+        <v>0.4258</v>
       </c>
       <c r="H12" t="n">
-        <v>2.093</v>
+        <v>2.0764</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6388</v>
+        <v>-1.6506</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0238</v>
+        <v>1.0543</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0343</v>
+        <v>1.047</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0105</v>
+        <v>0.0072</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5696</v>
+        <v>-0.6284</v>
       </c>
       <c r="N12" t="n">
-        <v>1.0587</v>
+        <v>1.0294</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6283</v>
+        <v>-1.6578</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.518</v>
+        <v>-1.0965</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9086</v>
+        <v>-0.6785</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6093</v>
+        <v>-0.4181</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6647</v>
+        <v>1.6921</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.509599999999999</v>
+        <v>9.890700000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5725</v>
+        <v>6.849900000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>3.937</v>
+        <v>3.0407</v>
       </c>
       <c r="G13" t="n">
-        <v>15.4946</v>
+        <v>15.527</v>
       </c>
       <c r="H13" t="n">
-        <v>14.9124</v>
+        <v>14.9237</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5822999999999998</v>
+        <v>0.6035000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>20.6246</v>
+        <v>21.1531</v>
       </c>
       <c r="K13" t="n">
-        <v>13.5233</v>
+        <v>13.8219</v>
       </c>
       <c r="L13" t="n">
-        <v>7.1013</v>
+        <v>7.331199999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.129900000000001</v>
+        <v>-5.6259</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3892</v>
+        <v>1.102</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.519000000000001</v>
+        <v>-6.727799999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.1211</v>
+        <v>-5.061400000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.4362</v>
+        <v>-18.2208</v>
       </c>
       <c r="R13" t="n">
-        <v>13.315</v>
+        <v>13.1595</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1671000000000002</v>
+        <v>0.1131</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2615</v>
+        <v>-0.8147</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0943</v>
+        <v>0.9276000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6965000000000002</v>
+        <v>-0.6883</v>
       </c>
       <c r="W13" t="n">
-        <v>4.6459</v>
+        <v>4.732099999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.3424</v>
+        <v>-5.4204</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0676</v>
+        <v>3.9015</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4664</v>
+        <v>3.4079</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6011</v>
+        <v>0.4936</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.569</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6702</v>
+        <v>0.7472</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2977</v>
+        <v>-1.3163</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7626</v>
+        <v>2.9068</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7336</v>
+        <v>2.8598</v>
       </c>
       <c r="L14" t="n">
-        <v>0.029</v>
+        <v>0.047</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.3901</v>
+        <v>-3.4758</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0634</v>
+        <v>-2.1126</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3267</v>
+        <v>-1.3633</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R14" t="n">
-        <v>3.0727</v>
+        <v>3.0368</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7146</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2849</v>
+        <v>-0.5229</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5703</v>
+        <v>0.5885</v>
       </c>
       <c r="V14" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="W14" t="n">
-        <v>2.013</v>
+        <v>2.0362</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3482</v>
+        <v>0.3442</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8191</v>
+        <v>2.605</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0691</v>
+        <v>4.2213</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.25</v>
+        <v>-1.6162</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3373</v>
+        <v>1.3087</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6303</v>
+        <v>-0.6512</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9675</v>
+        <v>1.9599</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2155</v>
+        <v>4.2474</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0148</v>
+        <v>1.0273</v>
       </c>
       <c r="L15" t="n">
-        <v>3.2007</v>
+        <v>3.2202</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.8782</v>
+        <v>-2.9388</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6451</v>
+        <v>-1.6785</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2332</v>
+        <v>-1.2602</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S15" t="n">
-        <v>0.29</v>
+        <v>0.1302</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1464</v>
+        <v>-0.0262</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4364</v>
+        <v>0.1563</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.837</v>
+        <v>0.7693</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5889</v>
+        <v>-1.0588</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7519</v>
+        <v>1.8281</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4716</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6893</v>
+        <v>-1.0678</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1609</v>
+        <v>1.1485</v>
       </c>
       <c r="J16" t="n">
-        <v>1.318</v>
+        <v>-0.0364</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6577</v>
+        <v>-0.752</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9758</v>
+        <v>0.7156</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8464</v>
+        <v>0.1171</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0316</v>
+        <v>-0.3158</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1852</v>
+        <v>0.433</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6145</v>
+        <v>1.2147</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6145</v>
+        <v>1.2147</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9314</v>
+        <v>0.1622</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2709</v>
+        <v>-0.3341</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3395</v>
+        <v>0.4962</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1806</v>
+        <v>-0.6883</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.6883</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MOLINA MARTINEZ</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.1959</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2428</v>
+        <v>1.8749</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6122</v>
+        <v>-1.6791</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2231</v>
+        <v>0.4621</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7926</v>
+        <v>-1.6995</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4305</v>
+        <v>2.1616</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0929</v>
+        <v>1.3352</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1034</v>
+        <v>-0.6526</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0105</v>
+        <v>1.9877</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.316</v>
+        <v>-0.8731</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.896</v>
+        <v>-1.0469</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.42</v>
+        <v>0.1738</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6388</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.663</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8666</v>
+        <v>0.3166</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9935</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1269</v>
+        <v>-0.2232</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3482</v>
+        <v>-1.1902</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8324</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>J. MOLINA MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6156</v>
+        <v>0.1815</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2044</v>
+        <v>0.3772</v>
       </c>
       <c r="F18" t="n">
-        <v>1.82</v>
+        <v>-0.1957</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0764</v>
+        <v>-2.2575</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0758</v>
+        <v>-1.8173</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1522</v>
+        <v>-0.4402</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0578</v>
+        <v>0.1251</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.769</v>
+        <v>0.1179</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7113</v>
+        <v>0.0072</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1342</v>
+        <v>-2.3826</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3068</v>
+        <v>-1.9352</v>
       </c>
       <c r="O18" t="n">
-        <v>0.441</v>
+        <v>-0.4474</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2291</v>
+        <v>1.6196</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2291</v>
+        <v>2.6319</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0065</v>
+        <v>0.4753</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4501</v>
+        <v>0.0741</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4567</v>
+        <v>0.4012</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6965</v>
+        <v>0.3442</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6965</v>
+        <v>1.1902</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.788</v>
+        <v>-0.2398</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9858</v>
+        <v>-1.2719</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1977</v>
+        <v>1.0321</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5955</v>
+        <v>1.6277</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.4646</v>
+        <v>-3.4595</v>
       </c>
       <c r="I19" t="n">
-        <v>5.06</v>
+        <v>5.0872</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8508</v>
+        <v>3.9487</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5128</v>
+        <v>-1.4652</v>
       </c>
       <c r="L19" t="n">
-        <v>5.3636</v>
+        <v>5.4139</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2553</v>
+        <v>-2.3211</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9518</v>
+        <v>-1.9943</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3035</v>
+        <v>-0.3267</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.4582</v>
+        <v>-2.4294</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R19" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1674</v>
+        <v>0.311</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9574</v>
+        <v>-0.4103</v>
       </c>
       <c r="U19" t="n">
-        <v>0.79</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. OSAIKHWUWUOMWAN</t>
+          <t>J. SOLER CIRUJEDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3294</v>
+        <v>-1.7415</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3297</v>
+        <v>-1.0902</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6591</v>
+        <v>-0.6513</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8331</v>
+        <v>-2.21</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8532</v>
+        <v>-1.1453</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9799</v>
+        <v>-1.0647</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1964</v>
+        <v>-0.1053</v>
       </c>
       <c r="K20" t="n">
-        <v>0.039</v>
+        <v>0.079</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2355</v>
+        <v>-0.1843</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6367</v>
+        <v>-2.1047</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8922</v>
+        <v>-1.2243</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.8804</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2048</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0242</v>
+        <v>-2.0245</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2989</v>
+        <v>-0.2561</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3698</v>
+        <v>-0.1507</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0709</v>
+        <v>-0.1054</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.5344</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1806</v>
+        <v>0.3442</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SOLER CIRUJEDA</t>
+          <t>C. OSAIKHWUWUOMWAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5461</v>
+        <v>-2.157</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5895</v>
+        <v>-0.4663</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9566</v>
+        <v>-1.6907</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2004</v>
+        <v>-2.8538</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1209</v>
+        <v>-0.869</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0795</v>
+        <v>-1.9849</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1405</v>
+        <v>-1.1857</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0781</v>
+        <v>0.0395</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2185</v>
+        <v>-1.2252</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0599</v>
+        <v>-1.6682</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.199</v>
+        <v>-0.9085</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8609</v>
+        <v>-0.7597</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8194</v>
+        <v>0.2025</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0485</v>
+        <v>-1.0123</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0552</v>
+        <v>0.4943</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5810999999999999</v>
+        <v>0.5414</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4741</v>
+        <v>-0.0471</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5288</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3482</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2501</v>
+        <v>-3.0825</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0036</v>
+        <v>-1.5358</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2465</v>
+        <v>-1.5467</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2686</v>
+        <v>-2.2816</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.5928</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6804</v>
+        <v>-1.6889</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6319</v>
+        <v>-0.6135</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0253</v>
+        <v>0.0388</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6572</v>
+        <v>-0.6523</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6367</v>
+        <v>-1.6682</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6135</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0232</v>
+        <v>-1.0365</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0429</v>
+        <v>0.1384</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5895</v>
+        <v>-0.161</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5466</v>
+        <v>0.2995</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9385</v>
+        <v>-0.9393</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1115</v>
+        <v>-3.7767</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4126</v>
+        <v>-3.6435</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6989</v>
+        <v>-0.1331</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.1941</v>
+        <v>-4.203</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.2994</v>
+        <v>-2.2933</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8946</v>
+        <v>-1.9097</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3242</v>
+        <v>-2.2746</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1282</v>
+        <v>-1.0892</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1959</v>
+        <v>-1.1854</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8699</v>
+        <v>-1.9284</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1712</v>
+        <v>-1.2041</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6987</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4203</v>
+        <v>-0.0356</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.3567</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3562</v>
+        <v>0.3211</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7262</v>
+        <v>-0.7528</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.7262</v>
+        <v>-0.7528</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4545</v>
+        <v>-4.8421</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4382</v>
+        <v>-3.8554</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0163</v>
+        <v>-0.9868</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.6286</v>
+        <v>-4.6314</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0683</v>
+        <v>-2.0752</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.5603</v>
+        <v>-2.5562</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.759</v>
+        <v>-2.7219</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.3155</v>
+        <v>-1.3052</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4435</v>
+        <v>-1.4167</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8696</v>
+        <v>-1.9096</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7529</v>
+        <v>-0.77</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1167</v>
+        <v>-1.1395</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8259</v>
+        <v>-0.2107</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.655</v>
+        <v>-0.1213</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.171</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.509799999999998</v>
+        <v>-8.186400000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.937199999999999</v>
+        <v>-3.040599999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.5727</v>
+        <v>-5.145799999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-15.4946</v>
+        <v>-15.5271</v>
       </c>
       <c r="H25" t="n">
-        <v>-14.9124</v>
+        <v>-14.9237</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5823000000000005</v>
+        <v>-0.6036999999999995</v>
       </c>
       <c r="J25" t="n">
-        <v>5.129999999999999</v>
+        <v>5.6258</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.389</v>
+        <v>-1.1019</v>
       </c>
       <c r="L25" t="n">
-        <v>6.519299999999999</v>
+        <v>6.727699999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-20.6246</v>
+        <v>-21.1534</v>
       </c>
       <c r="N25" t="n">
-        <v>-13.5235</v>
+        <v>-13.8218</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.1012</v>
+        <v>-7.331200000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>5.1211</v>
+        <v>5.0614</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.3149</v>
+        <v>-13.1596</v>
       </c>
       <c r="R25" t="n">
-        <v>18.4361</v>
+        <v>18.2209</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1671</v>
+        <v>1.5913</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0944</v>
+        <v>-0.9279000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>1.2614</v>
+        <v>2.519</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6963999999999997</v>
+        <v>0.6884</v>
       </c>
       <c r="W25" t="n">
-        <v>5.3425</v>
+        <v>5.420299999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.646100000000001</v>
+        <v>-4.7319</v>
       </c>
     </row>
   </sheetData>
